--- a/erp-server/erp-server-wms/src/main/resources/excel/pickingLists.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/pickingLists.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>拣货单号</t>
   </si>
@@ -46,18 +46,24 @@
     <t>库区</t>
   </si>
   <si>
-    <t>库位</t>
-  </si>
-  <si>
-    <t>暂存库区</t>
-  </si>
-  <si>
-    <t>暂存库位</t>
+    <t>拣货仓位</t>
   </si>
   <si>
     <t>数量</t>
   </si>
   <si>
+    <t>存放库区</t>
+  </si>
+  <si>
+    <t>存放仓位</t>
+  </si>
+  <si>
+    <t>更新人</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -76,13 +82,19 @@
     <t>{.warehouseLocation}</t>
   </si>
   <si>
+    <t>{.qty}</t>
+  </si>
+  <si>
     <t>{.stagingAreaName}</t>
   </si>
   <si>
     <t>{.stagingLocation}</t>
   </si>
   <si>
-    <t>{.qty}</t>
+    <t>{.updateUserName}</t>
+  </si>
+  <si>
+    <t>{.updateTime}</t>
   </si>
 </sst>
 </file>
@@ -95,7 +107,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,22 +127,6 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF4A4A4A"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF4A4A4A"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -622,137 +618,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -765,13 +761,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1130,7 +1120,8 @@
     <col min="3" max="3" width="27.375" customWidth="1"/>
     <col min="4" max="4" width="20.5" customWidth="1"/>
     <col min="5" max="6" width="20.75" customWidth="1"/>
-    <col min="7" max="9" width="13.875" customWidth="1"/>
+    <col min="7" max="8" width="13.875" customWidth="1"/>
+    <col min="9" max="9" width="18.5" customWidth="1"/>
     <col min="10" max="10" width="12.625" customWidth="1"/>
     <col min="11" max="11" width="42" customWidth="1"/>
     <col min="12" max="12" width="14.375" customWidth="1"/>
@@ -1169,17 +1160,21 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
@@ -1192,45 +1187,49 @@
       <c r="U1" s="3"/>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:21">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
+      <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/pickingLists.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/pickingLists.xlsx
@@ -1175,16 +1175,16 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+      <c r="O1"/>
+      <c r="P1"/>
+      <c r="Q1"/>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:21">
       <c r="A2" s="4" t="s">
